--- a/data/ds nhan vien.xlsx
+++ b/data/ds nhan vien.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\pm_chamcong_vantay_nguyenle\pm_haitran\bin\Debug\net9.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03EF3791-7548-4C5C-A531-677965E7824F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{CFAE8869-D588-493A-A04B-DD865F85AEB5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="458">
   <si>
     <t>Mã NV</t>
   </si>
@@ -1390,12 +1389,21 @@
   </si>
   <si>
     <t>13/12/2021 12:00:00 AM</t>
+  </si>
+  <si>
+    <t>Nguyễn Tiến Huy</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>NV0140</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1750,8 +1758,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91804826-B10B-4C41-9288-C17864A91317}">
-  <dimension ref="A1:H144"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -5507,6 +5515,26 @@
         <v>14</v>
       </c>
     </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
